--- a/diseases/d038/2005-2009.xlsx
+++ b/diseases/d038/2005-2009.xlsx
@@ -913,9 +913,6 @@
       <c r="O3" t="n">
         <v>89</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>1.696504172065934</v>
       </c>
@@ -1693,9 +1690,6 @@
       <c r="O7" t="n">
         <v>404</v>
       </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
       <c r="R7" t="n">
         <v>7.700985230501544</v>
       </c>
@@ -2473,9 +2467,6 @@
       <c r="O11" t="n">
         <v>1204</v>
       </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
       <c r="R11" t="n">
         <v>22.950460934465</v>
       </c>
@@ -3253,9 +3244,6 @@
       <c r="O15" t="n">
         <v>310</v>
       </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
       <c r="R15" t="n">
         <v>5.909171835285838</v>
       </c>
@@ -4033,9 +4021,6 @@
       <c r="O19" t="n">
         <v>49</v>
       </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
       <c r="R19" t="n">
         <v>0.9340303868677615</v>
       </c>
@@ -4813,9 +4798,6 @@
       <c r="O23" t="n">
         <v>9</v>
       </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
       <c r="R23" t="n">
         <v>0.1715566016695889</v>
       </c>
@@ -5593,9 +5575,6 @@
       <c r="O27" t="n">
         <v>0</v>
       </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
       <c r="R27" t="n">
         <v>0</v>
       </c>
@@ -6373,9 +6352,6 @@
       <c r="O31" t="n">
         <v>0</v>
       </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
       <c r="R31" t="n">
         <v>0</v>
       </c>
@@ -7153,9 +7129,6 @@
       <c r="O35" t="n">
         <v>0</v>
       </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
       <c r="R35" t="n">
         <v>0</v>
       </c>
@@ -7933,9 +7906,6 @@
       <c r="O39" t="n">
         <v>1</v>
       </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
       <c r="R39" t="n">
         <v>0.01906184462995432</v>
       </c>
@@ -8713,9 +8683,6 @@
       <c r="O43" t="n">
         <v>0</v>
       </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
       <c r="R43" t="n">
         <v>0</v>
       </c>
@@ -9493,9 +9460,6 @@
       <c r="O47" t="n">
         <v>4</v>
       </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
       <c r="R47" t="n">
         <v>0.07624737851981726</v>
       </c>
@@ -10273,9 +10237,6 @@
       <c r="O51" t="n">
         <v>28</v>
       </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
       <c r="R51" t="n">
         <v>0.5316879868802191</v>
       </c>
@@ -11053,9 +11014,6 @@
       <c r="O55" t="n">
         <v>162</v>
       </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
       <c r="R55" t="n">
         <v>3.076194781235554</v>
       </c>
@@ -11833,9 +11791,6 @@
       <c r="O59" t="n">
         <v>926</v>
       </c>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
       <c r="R59" t="n">
         <v>17.58368128039582</v>
       </c>
@@ -12613,9 +12568,6 @@
       <c r="O63" t="n">
         <v>636</v>
       </c>
-      <c r="Q63" t="n">
-        <v>0</v>
-      </c>
       <c r="R63" t="n">
         <v>12.07691284485069</v>
       </c>
@@ -13393,9 +13345,6 @@
       <c r="O67" t="n">
         <v>97</v>
       </c>
-      <c r="Q67" t="n">
-        <v>0</v>
-      </c>
       <c r="R67" t="n">
         <v>1.841919097406474</v>
       </c>
@@ -14173,9 +14122,6 @@
       <c r="O71" t="n">
         <v>9</v>
       </c>
-      <c r="Q71" t="n">
-        <v>0</v>
-      </c>
       <c r="R71" t="n">
         <v>0.1708997100686419</v>
       </c>
@@ -14953,9 +14899,6 @@
       <c r="O75" t="n">
         <v>1</v>
       </c>
-      <c r="Q75" t="n">
-        <v>0</v>
-      </c>
       <c r="R75" t="n">
         <v>0.01898885667429354</v>
       </c>
@@ -15733,9 +15676,6 @@
       <c r="O79" t="n">
         <v>1</v>
       </c>
-      <c r="Q79" t="n">
-        <v>0</v>
-      </c>
       <c r="R79" t="n">
         <v>0.01898885667429354</v>
       </c>
@@ -16513,9 +16453,6 @@
       <c r="O83" t="n">
         <v>1</v>
       </c>
-      <c r="Q83" t="n">
-        <v>0</v>
-      </c>
       <c r="R83" t="n">
         <v>0.01898885667429354</v>
       </c>
@@ -17293,9 +17230,6 @@
       <c r="O87" t="n">
         <v>0</v>
       </c>
-      <c r="Q87" t="n">
-        <v>0</v>
-      </c>
       <c r="R87" t="n">
         <v>0</v>
       </c>
@@ -18073,9 +18007,6 @@
       <c r="O91" t="n">
         <v>4</v>
       </c>
-      <c r="Q91" t="n">
-        <v>0</v>
-      </c>
       <c r="R91" t="n">
         <v>0.07595542669717416</v>
       </c>
@@ -18853,9 +18784,6 @@
       <c r="O95" t="n">
         <v>4</v>
       </c>
-      <c r="Q95" t="n">
-        <v>0</v>
-      </c>
       <c r="R95" t="n">
         <v>0.07595542669717416</v>
       </c>
@@ -19633,9 +19561,6 @@
       <c r="O99" t="n">
         <v>81</v>
       </c>
-      <c r="Q99" t="n">
-        <v>0</v>
-      </c>
       <c r="R99" t="n">
         <v>1.531564407955815</v>
       </c>
@@ -20413,9 +20338,6 @@
       <c r="O103" t="n">
         <v>827</v>
       </c>
-      <c r="Q103" t="n">
-        <v>0</v>
-      </c>
       <c r="R103" t="n">
         <v>15.6370835232032</v>
       </c>
@@ -21193,9 +21115,6 @@
       <c r="O107" t="n">
         <v>1024</v>
       </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
       <c r="R107" t="n">
         <v>19.36199942897228</v>
       </c>
@@ -21973,9 +21892,6 @@
       <c r="O111" t="n">
         <v>150</v>
       </c>
-      <c r="Q111" t="n">
-        <v>0</v>
-      </c>
       <c r="R111" t="n">
         <v>2.836230385103362</v>
       </c>
@@ -22753,9 +22669,6 @@
       <c r="O115" t="n">
         <v>13</v>
       </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
       <c r="R115" t="n">
         <v>0.2458066333756247</v>
       </c>
@@ -23533,9 +23446,6 @@
       <c r="O119" t="n">
         <v>4</v>
       </c>
-      <c r="Q119" t="n">
-        <v>0</v>
-      </c>
       <c r="R119" t="n">
         <v>0.07563281026942298</v>
       </c>
@@ -24313,9 +24223,6 @@
       <c r="O123" t="n">
         <v>1</v>
       </c>
-      <c r="Q123" t="n">
-        <v>0</v>
-      </c>
       <c r="R123" t="n">
         <v>0.01890820256735574</v>
       </c>
@@ -25093,9 +25000,6 @@
       <c r="O127" t="n">
         <v>0</v>
       </c>
-      <c r="Q127" t="n">
-        <v>0</v>
-      </c>
       <c r="R127" t="n">
         <v>0</v>
       </c>
@@ -25873,9 +25777,6 @@
       <c r="O131" t="n">
         <v>0</v>
       </c>
-      <c r="Q131" t="n">
-        <v>0</v>
-      </c>
       <c r="R131" t="n">
         <v>0</v>
       </c>
@@ -26653,9 +26554,6 @@
       <c r="O135" t="n">
         <v>2</v>
       </c>
-      <c r="Q135" t="n">
-        <v>0</v>
-      </c>
       <c r="R135" t="n">
         <v>0.03781640513471149</v>
       </c>
@@ -27433,9 +27331,6 @@
       <c r="O139" t="n">
         <v>7</v>
       </c>
-      <c r="Q139" t="n">
-        <v>0</v>
-      </c>
       <c r="R139" t="n">
         <v>0.1323574179714902</v>
       </c>
@@ -28213,9 +28108,6 @@
       <c r="O143" t="n">
         <v>73</v>
       </c>
-      <c r="Q143" t="n">
-        <v>0</v>
-      </c>
       <c r="R143" t="n">
         <v>1.380298787416969</v>
       </c>
@@ -28993,9 +28885,6 @@
       <c r="O147" t="n">
         <v>848</v>
       </c>
-      <c r="Q147" t="n">
-        <v>0</v>
-      </c>
       <c r="R147" t="n">
         <v>15.95971827333163</v>
       </c>
@@ -29773,9 +29662,6 @@
       <c r="O151" t="n">
         <v>1470</v>
       </c>
-      <c r="Q151" t="n">
-        <v>0</v>
-      </c>
       <c r="R151" t="n">
         <v>27.66602106344045</v>
       </c>
@@ -30553,9 +30439,6 @@
       <c r="O155" t="n">
         <v>790</v>
       </c>
-      <c r="Q155" t="n">
-        <v>0</v>
-      </c>
       <c r="R155" t="n">
         <v>14.86813376878772</v>
       </c>
@@ -31333,9 +31216,6 @@
       <c r="O159" t="n">
         <v>378</v>
       </c>
-      <c r="Q159" t="n">
-        <v>0</v>
-      </c>
       <c r="R159" t="n">
         <v>7.114119702027543</v>
       </c>
@@ -32113,9 +31993,6 @@
       <c r="O163" t="n">
         <v>84</v>
       </c>
-      <c r="Q163" t="n">
-        <v>0</v>
-      </c>
       <c r="R163" t="n">
         <v>1.580915489339454</v>
       </c>
@@ -32893,9 +32770,6 @@
       <c r="O167" t="n">
         <v>5</v>
       </c>
-      <c r="Q167" t="n">
-        <v>0</v>
-      </c>
       <c r="R167" t="n">
         <v>0.09410211246068179</v>
       </c>
@@ -33673,9 +33547,6 @@
       <c r="O171" t="n">
         <v>1</v>
       </c>
-      <c r="Q171" t="n">
-        <v>0</v>
-      </c>
       <c r="R171" t="n">
         <v>0.01882042249213636</v>
       </c>
@@ -34453,9 +34324,6 @@
       <c r="O175" t="n">
         <v>1</v>
       </c>
-      <c r="Q175" t="n">
-        <v>0</v>
-      </c>
       <c r="R175" t="n">
         <v>0.01882042249213636</v>
       </c>
@@ -35233,9 +35101,6 @@
       <c r="O179" t="n">
         <v>1</v>
       </c>
-      <c r="Q179" t="n">
-        <v>0</v>
-      </c>
       <c r="R179" t="n">
         <v>0.01882042249213636</v>
       </c>
@@ -36013,9 +35878,6 @@
       <c r="O183" t="n">
         <v>2</v>
       </c>
-      <c r="Q183" t="n">
-        <v>0</v>
-      </c>
       <c r="R183" t="n">
         <v>0.03764084498427271</v>
       </c>
@@ -36793,9 +36655,6 @@
       <c r="O187" t="n">
         <v>5</v>
       </c>
-      <c r="Q187" t="n">
-        <v>0</v>
-      </c>
       <c r="R187" t="n">
         <v>0.09410211246068179</v>
       </c>
@@ -37573,9 +37432,6 @@
       <c r="O191" t="n">
         <v>155</v>
       </c>
-      <c r="Q191" t="n">
-        <v>0</v>
-      </c>
       <c r="R191" t="n">
         <v>2.917165486281135</v>
       </c>
@@ -38353,9 +38209,6 @@
       <c r="O195" t="n">
         <v>1301</v>
       </c>
-      <c r="Q195" t="n">
-        <v>0</v>
-      </c>
       <c r="R195" t="n">
         <v>24.36851411908149</v>
       </c>
@@ -39611,9 +39464,6 @@
       <c r="O201" t="n">
         <v>1700</v>
       </c>
-      <c r="Q201" t="n">
-        <v>0</v>
-      </c>
       <c r="R201" t="n">
         <v>31.84202459833861</v>
       </c>
@@ -40391,9 +40241,6 @@
       <c r="O205" t="n">
         <v>591</v>
       </c>
-      <c r="Q205" t="n">
-        <v>0</v>
-      </c>
       <c r="R205" t="n">
         <v>11.06978619859889</v>
       </c>
@@ -41171,9 +41018,6 @@
       <c r="O209" t="n">
         <v>314</v>
       </c>
-      <c r="Q209" t="n">
-        <v>0</v>
-      </c>
       <c r="R209" t="n">
         <v>5.881409249340191</v>
       </c>
@@ -41951,9 +41795,6 @@
       <c r="O213" t="n">
         <v>77</v>
       </c>
-      <c r="Q213" t="n">
-        <v>0</v>
-      </c>
       <c r="R213" t="n">
         <v>1.44225640827769</v>
       </c>
@@ -42731,9 +42572,6 @@
       <c r="O217" t="n">
         <v>73</v>
       </c>
-      <c r="Q217" t="n">
-        <v>0</v>
-      </c>
       <c r="R217" t="n">
         <v>1.36733399745807</v>
       </c>
@@ -43511,9 +43349,6 @@
       <c r="O221" t="n">
         <v>170</v>
       </c>
-      <c r="Q221" t="n">
-        <v>0</v>
-      </c>
       <c r="R221" t="n">
         <v>3.184202459833862</v>
       </c>
@@ -44291,9 +44126,6 @@
       <c r="O225" t="n">
         <v>58</v>
       </c>
-      <c r="Q225" t="n">
-        <v>0</v>
-      </c>
       <c r="R225" t="n">
         <v>1.086374956884494</v>
       </c>
@@ -45071,9 +44903,6 @@
       <c r="O229" t="n">
         <v>86</v>
       </c>
-      <c r="Q229" t="n">
-        <v>0</v>
-      </c>
       <c r="R229" t="n">
         <v>1.610831832621836</v>
       </c>
@@ -45851,9 +45680,6 @@
       <c r="O233" t="n">
         <v>1231</v>
       </c>
-      <c r="Q233" t="n">
-        <v>0</v>
-      </c>
       <c r="R233" t="n">
         <v>23.05737192973814</v>
       </c>
@@ -46631,9 +46457,6 @@
       <c r="O237" t="n">
         <v>7499</v>
       </c>
-      <c r="Q237" t="n">
-        <v>0</v>
-      </c>
       <c r="R237" t="n">
         <v>140.4607896840831</v>
       </c>
@@ -47410,9 +47233,6 @@
       </c>
       <c r="O241" t="n">
         <v>336</v>
-      </c>
-      <c r="Q241" t="n">
-        <v>0</v>
       </c>
       <c r="R241" t="n">
         <v>6.293482508848102</v>
